--- a/School_Mang/EXCEL/Final/Term_B/Term_B_2_Test.xlsx
+++ b/School_Mang/EXCEL/Final/Term_B/Term_B_2_Test.xlsx
@@ -167,29 +167,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF8B8B"/>
-          <bgColor rgb="FFFADF53"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC5C5"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="3">
     <dxf>
       <fill>
         <patternFill>
@@ -524,7 +502,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:J152"/>
+  <dimension ref="A2:AD152"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="0" style="1" hidden="1" customWidth="1"/>
@@ -533,7 +511,7 @@
     <col min="11" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B2" s="11"/>
       <c r="C2" s="11"/>
       <c r="D2" s="11"/>
@@ -544,7 +522,7 @@
       <c r="I2" s="11"/>
       <c r="J2" s="11"/>
     </row>
-    <row r="3" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:30" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B3" s="8"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -555,7 +533,7 @@
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -587,7 +565,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B5" s="10"/>
       <c r="C5" s="6">
         <v>0</v>
@@ -614,7 +592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B6" s="10"/>
       <c r="C6" s="6">
         <v>0</v>
@@ -641,7 +619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B7" s="10"/>
       <c r="C7" s="5">
         <v>0</v>
@@ -668,7 +646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B8" s="10"/>
       <c r="C8" s="5">
         <v>0</v>
@@ -694,8 +672,12 @@
       <c r="J8" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="AD8" s="1">
+        <f>SUM(C5:J20)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B9" s="10"/>
       <c r="C9" s="5">
         <v>0</v>
@@ -722,7 +704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B10" s="10"/>
       <c r="C10" s="5">
         <v>0</v>
@@ -749,7 +731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B11" s="10"/>
       <c r="C11" s="5">
         <v>0</v>
@@ -776,7 +758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B12" s="10"/>
       <c r="C12" s="5">
         <v>0</v>
@@ -803,7 +785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B13" s="10"/>
       <c r="C13" s="5">
         <v>0</v>
@@ -830,7 +812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B14" s="10"/>
       <c r="C14" s="5">
         <v>0</v>
@@ -857,7 +839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B15" s="10"/>
       <c r="C15" s="5">
         <v>0</v>
@@ -884,7 +866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B16" s="10"/>
       <c r="C16" s="5">
         <v>0</v>

--- a/School_Mang/EXCEL/Final/Term_B/Term_B_2_Test.xlsx
+++ b/School_Mang/EXCEL/Final/Term_B/Term_B_2_Test.xlsx
@@ -167,7 +167,29 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="6">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF8B8B"/>
+          <bgColor rgb="FFFADF53"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC5C5"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -4571,16 +4593,16 @@
     <mergeCell ref="B2:J2"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:J152">
-    <cfRule type="containsBlanks" dxfId="2" priority="3">
+    <cfRule type="containsBlanks" dxfId="5" priority="3">
       <formula>LEN(TRIM(B5))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C5:J152">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="20" operator="greaterThan">
-      <formula>30</formula>
+    <cfRule type="cellIs" dxfId="3" priority="20" operator="greaterThan">
+      <formula>60</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
